--- a/data/trans_orig/P0801-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2007</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228623</t>
+          <t>228454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249673</t>
+          <t>249282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199559</t>
+          <t>198561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223892</t>
+          <t>224491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435385</t>
+          <t>433679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468605</t>
+          <t>469278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56613</t>
+          <t>57165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56658</t>
+          <t>56154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88509</t>
+          <t>88176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415827</t>
+          <t>417024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446252</t>
+          <t>445480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361863</t>
+          <t>363500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>400323</t>
+          <t>399598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>787949</t>
+          <t>789644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>837947</t>
+          <t>838647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56216</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104168</t>
+          <t>106115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110475</t>
+          <t>110891</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154318</t>
+          <t>151571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49251</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40458</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70423</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283657</t>
+          <t>284156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303124</t>
+          <t>303510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>248704</t>
+          <t>250048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278686</t>
+          <t>277246</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>539830</t>
+          <t>540494</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>576270</t>
+          <t>576363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70600</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60844</t>
+          <t>61509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>93164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23710</t>
+          <t>24253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>314031</t>
+          <t>312317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>334555</t>
+          <t>334562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>278940</t>
+          <t>277535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>308625</t>
+          <t>309130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>601358</t>
+          <t>602616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>638404</t>
+          <t>641423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47691</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75066</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>101465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180337</t>
+          <t>180284</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194092</t>
+          <t>194321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>161053</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>182510</t>
+          <t>181838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347326</t>
+          <t>346064</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>373811</t>
+          <t>372982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>45870</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231463</t>
+          <t>231265</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250737</t>
+          <t>250647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193097</t>
+          <t>193420</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>223529</t>
+          <t>223271</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>427900</t>
+          <t>433407</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>466558</t>
+          <t>466875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41932</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69050</t>
+          <t>70154</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66333</t>
+          <t>65764</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102727</t>
+          <t>97491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25244</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>522606</t>
+          <t>522596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>553248</t>
+          <t>554855</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>481952</t>
+          <t>480060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>521947</t>
+          <t>521234</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1013943</t>
+          <t>1015999</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1067436</t>
+          <t>1067815</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>42655</t>
+          <t>42030</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69969</t>
+          <t>69867</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>80350</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117158</t>
+          <t>115914</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129717</t>
+          <t>130989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175613</t>
+          <t>180085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>30649</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>51537</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>45667</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>75364</t>
+          <t>74889</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>627487</t>
+          <t>630701</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>663443</t>
+          <t>663756</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>594145</t>
+          <t>593186</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>641300</t>
+          <t>638987</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1234149</t>
+          <t>1236048</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1293574</t>
+          <t>1296818</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>46035</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75710</t>
+          <t>75977</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,82 +4053,82 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>118796</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>100190</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>142425</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>18,18%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>179242</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>155548</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>207272</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>10,18%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>118796</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>99652</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>142028</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>179242</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>154888</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>204480</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48364</t>
+          <t>49889</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>60023</t>
+          <t>60393</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>66964</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>103429</t>
+          <t>100826</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2876172</t>
+          <t>2876209</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2943079</t>
+          <t>2946110</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2603467</t>
+          <t>2605295</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2703467</t>
+          <t>2701280</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5500015</t>
+          <t>5510525</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5624881</t>
+          <t>5624915</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>235373</t>
+          <t>233979</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>294603</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>499517</t>
+          <t>501078</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>582911</t>
+          <t>587800</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>751247</t>
+          <t>751730</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>859559</t>
+          <t>855295</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>84180</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>120021</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>250157</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>316877</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2012</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>231292</t>
+          <t>230704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257985</t>
+          <t>256611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189515</t>
+          <t>188881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220814</t>
+          <t>220145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>429516</t>
+          <t>429469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>469839</t>
+          <t>470962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43919</t>
+          <t>44547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>61114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63327</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98506</t>
+          <t>99660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27647</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46921</t>
+          <t>46718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>39305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65107</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409211</t>
+          <t>411495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447240</t>
+          <t>446043</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>358620</t>
+          <t>359084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>400577</t>
+          <t>400972</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783394</t>
+          <t>782299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>842025</t>
+          <t>835284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52921</t>
+          <t>53125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68028</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102778</t>
+          <t>102493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>102393</t>
+          <t>104151</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147997</t>
+          <t>147443</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>52258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75184</t>
+          <t>73989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76274</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114301</t>
+          <t>115980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>262126</t>
+          <t>260596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289015</t>
+          <t>289518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>243219</t>
+          <t>243242</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>276488</t>
+          <t>276407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>517543</t>
+          <t>516975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>559176</t>
+          <t>558105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42392</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72737</t>
+          <t>72028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103202</t>
+          <t>103758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34455</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56716</t>
+          <t>57444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301002</t>
+          <t>304421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>332647</t>
+          <t>332003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>249638</t>
+          <t>250260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>287969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>564278</t>
+          <t>563403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>611543</t>
+          <t>609985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48992</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77605</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77184</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113888</t>
+          <t>112176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45496</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>74105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64230</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>97824</t>
+          <t>99779</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164719</t>
+          <t>163928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188056</t>
+          <t>188123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143091</t>
+          <t>140378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>170260</t>
+          <t>169953</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316625</t>
+          <t>314892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>351085</t>
+          <t>350862</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18616</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29924</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>54501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>55419</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>86783</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>210554</t>
+          <t>211055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236549</t>
+          <t>236385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>189125</t>
+          <t>187377</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>218415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>406275</t>
+          <t>409027</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>447996</t>
+          <t>445525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,42%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44507</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41725</t>
+          <t>41643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66833</t>
+          <t>68900</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71077</t>
+          <t>72180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106304</t>
+          <t>105653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52940</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>563128</t>
+          <t>563368</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>598230</t>
+          <t>598712</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>506431</t>
+          <t>508634</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>552729</t>
+          <t>553722</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1084537</t>
+          <t>1080934</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1141927</t>
+          <t>1139993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>42410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71105</t>
+          <t>71810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87742</t>
+          <t>89099</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125901</t>
+          <t>126382</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138472</t>
+          <t>139944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>188535</t>
+          <t>187876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>42512</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73911</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64934</t>
+          <t>64471</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103389</t>
+          <t>103703</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>645401</t>
+          <t>648860</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>687105</t>
+          <t>689154</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>624839</t>
+          <t>624902</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>672242</t>
+          <t>674246</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1283179</t>
+          <t>1282108</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1346290</t>
+          <t>1349199</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>71727</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>109149</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>108387</t>
+          <t>107204</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>149029</t>
+          <t>148467</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>186635</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>246789</t>
+          <t>246146</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36008</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62015</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>54747</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>89670</t>
+          <t>88932</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2881909</t>
+          <t>2881731</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2967223</t>
+          <t>2967405</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2603398</t>
+          <t>2608515</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2709062</t>
+          <t>2712998</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5504372</t>
+          <t>5513816</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5646540</t>
+          <t>5647275</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>301580</t>
+          <t>299585</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>369805</t>
+          <t>371052</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>535995</t>
+          <t>534866</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>626076</t>
+          <t>625028</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>857992</t>
+          <t>855193</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>977917</t>
+          <t>975111</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>139269</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>192022</t>
+          <t>194331</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>287872</t>
+          <t>286207</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>355099</t>
+          <t>356685</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>442895</t>
+          <t>443843</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>533913</t>
+          <t>531141</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2016</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222936</t>
+          <t>223999</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>250434</t>
+          <t>251435</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192044</t>
+          <t>191214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223072</t>
+          <t>222728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>422463</t>
+          <t>423413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>466365</t>
+          <t>467810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52612</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59546</t>
+          <t>61001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96309</t>
+          <t>96281</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27677</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30278</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>55614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76562</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426486</t>
+          <t>427320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>455444</t>
+          <t>456404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>392311</t>
+          <t>391772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432218</t>
+          <t>431186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>832863</t>
+          <t>829589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880949</t>
+          <t>880446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>55747</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53663</t>
+          <t>54627</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88315</t>
+          <t>86531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91991</t>
+          <t>91487</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>132264</t>
+          <t>133085</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28228</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55684</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43450</t>
+          <t>43536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>76085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263156</t>
+          <t>264452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285444</t>
+          <t>286392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252422</t>
+          <t>252608</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>285310</t>
+          <t>283824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>524205</t>
+          <t>527239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562452</t>
+          <t>564157</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28107</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>49043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>37505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65674</t>
+          <t>66227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71998</t>
+          <t>71048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>105035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27110</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>301130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>330131</t>
+          <t>329246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>266593</t>
+          <t>265409</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304302</t>
+          <t>302948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>579121</t>
+          <t>579949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>626785</t>
+          <t>626910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>67095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>57608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>90160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>36916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65340</t>
+          <t>67049</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63857</t>
+          <t>63027</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101624</t>
+          <t>100126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174592</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>192282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157286</t>
+          <t>156288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181971</t>
+          <t>180721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337468</t>
+          <t>337802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>368543</t>
+          <t>370140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>29153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51884</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48092</t>
+          <t>47313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>75845</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>17090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194464</t>
+          <t>195666</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>222217</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172386</t>
+          <t>171389</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203847</t>
+          <t>202445</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>373279</t>
+          <t>376376</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>416835</t>
+          <t>417757</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36183</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35286</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>58057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90793</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>41554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51401</t>
+          <t>51219</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>82352</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>547842</t>
+          <t>550464</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>585775</t>
+          <t>584102</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>518673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>564412</t>
+          <t>563122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1079038</t>
+          <t>1080677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1139277</t>
+          <t>1138905</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52821</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>87092</t>
+          <t>85282</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>63275</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>98202</t>
+          <t>98241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>126051</t>
+          <t>123801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175898</t>
+          <t>173439</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31238</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51338</t>
+          <t>53133</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84380</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>68062</t>
+          <t>70641</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>108728</t>
+          <t>108902</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>668468</t>
+          <t>670474</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>704157</t>
+          <t>704289</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>637426</t>
+          <t>640274</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>687018</t>
+          <t>686876</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1320129</t>
+          <t>1321894</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1380147</t>
+          <t>1382805</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>104742</t>
+          <t>102247</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>146675</t>
+          <t>147174</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>170596</t>
+          <t>168039</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>226653</t>
+          <t>223517</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54505</t>
+          <t>52590</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77263</t>
+          <t>73668</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2881758</t>
+          <t>2877214</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2960466</t>
+          <t>2961766</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2689490</t>
+          <t>2690030</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2795589</t>
+          <t>2792964</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5595361</t>
+          <t>5599692</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5727800</t>
+          <t>5733595</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>292558</t>
+          <t>289822</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>362239</t>
+          <t>361242</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>457093</t>
+          <t>458988</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>543704</t>
+          <t>543207</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>772737</t>
+          <t>768341</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>876990</t>
+          <t>881772</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>124595</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>171432</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>265319</t>
+          <t>266832</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>336190</t>
+          <t>336917</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>404263</t>
+          <t>404517</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>493691</t>
+          <t>486863</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2023</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>250014</t>
+          <t>250486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>276330</t>
+          <t>277162</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223650</t>
+          <t>223277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243397</t>
+          <t>243610</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>482032</t>
+          <t>482167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>513437</t>
+          <t>513327</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54338</t>
+          <t>54664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>55767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72395</t>
+          <t>72275</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102088</t>
+          <t>101546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23628</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413626</t>
+          <t>416377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451182</t>
+          <t>452475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377295</t>
+          <t>376167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>410268</t>
+          <t>406847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>802008</t>
+          <t>801755</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>850453</t>
+          <t>851251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>51159</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86135</t>
+          <t>83785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94963</t>
+          <t>95617</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128112</t>
+          <t>127296</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>169489</t>
+          <t>171220</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51106</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>70384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263780</t>
+          <t>263803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>284314</t>
+          <t>284525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>270019</t>
+          <t>269566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>291083</t>
+          <t>291765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>541515</t>
+          <t>541526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>570697</t>
+          <t>572330</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46380</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63475</t>
+          <t>63629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24537</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39995</t>
+          <t>39673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236466</t>
+          <t>236602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266780</t>
+          <t>267491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>365503</t>
+          <t>363251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>427286</t>
+          <t>423440</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>615641</t>
+          <t>615378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>683785</t>
+          <t>681895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>46253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34442</t>
+          <t>37268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77993</t>
+          <t>79735</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68480</t>
+          <t>67211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113742</t>
+          <t>114524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>38565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>68041</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149971</t>
+          <t>149893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163165</t>
+          <t>163061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193577</t>
+          <t>193955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>231540</t>
+          <t>231449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351553</t>
+          <t>351367</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>388799</t>
+          <t>386883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>23885</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51451</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37907</t>
+          <t>39610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68166</t>
+          <t>69077</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>16273</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>232837</t>
+          <t>232370</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>248871</t>
+          <t>248093</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>204252</t>
+          <t>204691</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221006</t>
+          <t>221808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>444121</t>
+          <t>443037</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>466419</t>
+          <t>466070</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41437</t>
+          <t>42419</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>30627</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>48695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>502934</t>
+          <t>504463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>542220</t>
+          <t>540313</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>639743</t>
+          <t>640198</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>767852</t>
+          <t>781107</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1169054</t>
+          <t>1164458</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314122</t>
+          <t>1308880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>63479</t>
+          <t>62351</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>98353</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48179</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>130187</t>
+          <t>130304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>106358</t>
+          <t>113178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>209466</t>
+          <t>213909</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82652</t>
+          <t>82235</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51807</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102188</t>
+          <t>102238</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>266311</t>
+          <t>266933</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>812055</t>
+          <t>813324</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>520446</t>
+          <t>522291</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>560173</t>
+          <t>560490</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>704795</t>
+          <t>707039</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1342401</t>
+          <t>1344879</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>82439</t>
+          <t>80121</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>652459</t>
+          <t>646244</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>95823</t>
+          <t>96941</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>131607</t>
+          <t>132215</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>200993</t>
+          <t>198534</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>882869</t>
+          <t>879933</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>53170</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>76754</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>58636</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>111663</t>
+          <t>112565</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2137231</t>
+          <t>2152743</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2964823</t>
+          <t>2967652</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2887911</t>
+          <t>2883793</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3092455</t>
+          <t>3098624</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4965288</t>
+          <t>5036625</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5942834</t>
+          <t>5942376</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>342667</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1223273</t>
+          <t>1199362</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>400445</t>
+          <t>392132</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>535604</t>
+          <t>538496</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>816643</t>
+          <t>821386</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1839966</t>
+          <t>1734167</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>110518</t>
+          <t>107734</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>165951</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>216236</t>
+          <t>220567</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>295695</t>
+          <t>298997</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>357799</t>
+          <t>353317</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>452106</t>
+          <t>451446</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
